--- a/public/downloads/UMO_name-tags_template.xlsx
+++ b/public/downloads/UMO_name-tags_template.xlsx
@@ -82,8 +82,7 @@
       </c>
       <c r="C2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Продавец-консультант
-новых автомобилей</t>
+          <t xml:space="preserve">Продавец-консультант новых автомобилей</t>
         </is>
       </c>
     </row>
